--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6123-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6123-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD2DC6F6-065E-49D2-BB61-3CC80BBBB339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B669479-6E06-4DE0-8A51-B7B937BA5C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{3D327AB5-31A3-4508-878E-6F7D477EBBE7}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E5EA78E3-BBD9-4113-8815-947424837F9A}"/>
   </bookViews>
   <sheets>
     <sheet name="6123-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1624,28 +1624,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D342E7EB-2E74-49BF-9370-0A7E3C8082AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB0F792-B007-4525-982D-3888CA4D8A91}">
   <dimension ref="A1:X68"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1715,7 +1715,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1835,7 +1835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1943,7 +1943,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>30</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>30</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2024</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>8.2100000000000009</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>30</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>30</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="51">
         <v>2023</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>30</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>30</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>30</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>30</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>30</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>2022</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>30</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>30</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
         <v>30</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>30</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>30</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2021</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>30</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>30</v>
       </c>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>30</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>30</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>30</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="49">
         <v>2020</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
         <v>30</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>30</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>30</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
         <v>30</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="18" t="s">
         <v>30</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="51">
         <v>2019</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>30</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>30</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>30</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="53">
         <v>2018</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="55"/>
       <c r="B46" s="56"/>
       <c r="C46" s="22" t="s">
@@ -4843,7 +4843,7 @@
       <c r="W46" s="62"/>
       <c r="X46" s="58"/>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="51">
         <v>2017</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>2016</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="55"/>
       <c r="B49" s="56"/>
       <c r="C49" s="22" t="s">
@@ -5015,7 +5015,7 @@
       <c r="W49" s="62"/>
       <c r="X49" s="58"/>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="51">
         <v>2015</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="49">
         <v>2014</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="51">
         <v>2013</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="49">
         <v>2012</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>8.24</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="51">
         <v>2011</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="49">
         <v>2010</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="51">
         <v>2009</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="49">
         <v>2008</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="51">
         <v>2007</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="49">
         <v>2006</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="51">
         <v>2005</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="49">
         <v>2004</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="51">
         <v>2003</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="49">
         <v>2002</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="51">
         <v>2001</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="49">
         <v>2000</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="51">
         <v>1999</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="49">
         <v>1998</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="51" t="s">
         <v>69</v>
       </c>
